--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T11:44:16+00:00</t>
+    <t>2026-07-15T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:32:02+00:00</t>
+    <t>2026-07-15T14:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:55:56+00:00</t>
+    <t>2026-07-16T09:23:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$57</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="427">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T09:23:28+00:00</t>
+    <t>2026-07-17T06:35:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -646,6 +646,22 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension:entered-in-error</t>
+  </si>
+  <si>
+    <t>entered-in-error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-entered-in-error}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA Entered In Error</t>
+  </si>
+  <si>
+    <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
   </si>
   <si>
     <t>AllergyIntolerance.modifierExtension</t>
@@ -1671,12 +1687,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:AM57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.27734375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="36.9609375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.48828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3826,43 +3842,41 @@
         <v>202</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="D20" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3910,7 +3924,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3919,13 +3933,13 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3943,38 +3957,38 @@
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4023,7 +4037,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4035,24 +4049,24 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>214</v>
+        <v>21</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>215</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4060,33 +4074,35 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>21</v>
       </c>
@@ -4110,13 +4126,13 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>221</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -4134,36 +4150,36 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>222</v>
+        <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4186,16 +4202,16 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4224,10 +4240,10 @@
         <v>160</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4245,7 +4261,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4254,59 +4270,59 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4335,10 +4351,10 @@
         <v>160</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4356,7 +4372,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4365,31 +4381,31 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4411,13 +4427,13 @@
         <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4446,10 +4462,10 @@
         <v>160</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4467,13 +4483,13 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
@@ -4482,25 +4498,25 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4522,13 +4538,13 @@
         <v>168</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4557,10 +4573,10 @@
         <v>160</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4578,13 +4594,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4593,35 +4609,35 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
@@ -4630,16 +4646,16 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4665,13 +4681,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4689,7 +4705,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4704,52 +4720,54 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>21</v>
+        <v>267</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>101</v>
+        <v>222</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>102</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4774,13 +4792,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>21</v>
+        <v>271</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>272</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4798,7 +4816,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>104</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4810,35 +4828,35 @@
         <v>21</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>105</v>
+        <v>273</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>21</v>
+        <v>275</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4850,17 +4868,15 @@
         <v>21</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4897,31 +4913,31 @@
         <v>21</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>105</v>
@@ -4935,21 +4951,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4958,23 +4974,21 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>109</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>110</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
       </c>
@@ -5010,19 +5024,19 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>115</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5034,24 +5048,24 @@
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>279</v>
+        <v>105</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>280</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5059,10 +5073,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5074,19 +5088,19 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O31" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5135,13 +5149,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5150,35 +5164,35 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
@@ -5187,16 +5201,20 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>291</v>
+        <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5244,10 +5262,10 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>87</v>
@@ -5259,50 +5277,50 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL32" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>297</v>
-      </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>21</v>
+        <v>295</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5353,10 +5371,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>87</v>
@@ -5368,21 +5386,21 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5405,13 +5423,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5462,7 +5480,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5477,21 +5495,21 @@
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM34" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>309</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5499,13 +5517,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5514,13 +5532,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5571,7 +5589,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5586,25 +5604,25 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AL35" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="AM35" t="s" s="2">
-        <v>315</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>317</v>
+        <v>21</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5623,13 +5641,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5680,7 +5698,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5695,54 +5713,52 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" hidden="true">
-      <c r="A37" t="s" s="2">
-        <v>323</v>
-      </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L37" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>328</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5791,7 +5807,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5806,32 +5822,32 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>331</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>21</v>
+        <v>329</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>21</v>
@@ -5840,19 +5856,19 @@
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5902,7 +5918,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5917,13 +5933,13 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -5954,16 +5970,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6019,7 +6035,7 @@
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>21</v>
@@ -6028,21 +6044,21 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>343</v>
-      </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6050,13 +6066,13 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6065,15 +6081,17 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6122,7 +6140,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6146,7 +6164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>348</v>
       </c>
@@ -6159,13 +6177,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6174,13 +6192,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>101</v>
+        <v>349</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>102</v>
+        <v>350</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>103</v>
+        <v>351</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6231,22 +6249,22 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>104</v>
+        <v>348</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>105</v>
+        <v>352</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -6257,10 +6275,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6268,11 +6286,11 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G42" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
       </c>
@@ -6283,13 +6301,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6328,32 +6346,34 @@
         <v>21</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6362,16 +6382,14 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>351</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6380,10 +6398,10 @@
         <v>87</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>21</v>
@@ -6392,13 +6410,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>352</v>
+        <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>193</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
+        <v>194</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6437,16 +6455,14 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>115</v>
@@ -6458,7 +6474,7 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>116</v>
@@ -6473,48 +6489,46 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>108</v>
+        <v>357</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>205</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6562,7 +6576,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>359</v>
+        <v>115</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6571,13 +6585,13 @@
         <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6595,37 +6609,39 @@
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>21</v>
+        <v>361</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>108</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6649,74 +6665,74 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Z45" t="s" s="2">
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AA45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>367</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -6725,16 +6741,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6763,10 +6779,10 @@
         <v>153</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6784,13 +6800,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -6799,35 +6815,35 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>239</v>
+        <v>371</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -6836,16 +6852,16 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>101</v>
+        <v>222</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6871,13 +6887,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>21</v>
+        <v>377</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -6895,13 +6911,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -6910,32 +6926,32 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>380</v>
+        <v>244</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>21</v>
+        <v>379</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>21</v>
+        <v>381</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -6947,7 +6963,7 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>310</v>
+        <v>101</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>382</v>
@@ -6955,7 +6971,9 @@
       <c r="M48" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="N48" s="2"/>
+      <c r="N48" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7004,7 +7022,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7019,21 +7037,21 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>384</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7044,7 +7062,7 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>21</v>
@@ -7056,17 +7074,15 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>168</v>
+        <v>315</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N49" t="s" s="2">
         <v>388</v>
       </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
@@ -7091,13 +7107,13 @@
         <v>21</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>389</v>
+        <v>21</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>390</v>
+        <v>21</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>21</v>
@@ -7115,7 +7131,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7130,21 +7146,21 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>21</v>
+        <v>389</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7167,16 +7183,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7202,14 +7218,14 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>396</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7226,7 +7242,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7241,7 +7257,7 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>397</v>
+        <v>263</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
@@ -7252,10 +7268,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7266,7 +7282,7 @@
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7278,16 +7294,16 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>338</v>
+        <v>222</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7313,13 +7329,13 @@
         <v>21</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>21</v>
+        <v>400</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>21</v>
@@ -7337,13 +7353,13 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>21</v>
@@ -7352,7 +7368,7 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>342</v>
+        <v>402</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7363,10 +7379,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7389,15 +7405,17 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>101</v>
+        <v>343</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>102</v>
+        <v>404</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -7446,22 +7464,22 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>104</v>
+        <v>403</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>105</v>
+        <v>347</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7472,21 +7490,21 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>21</v>
@@ -7498,17 +7516,15 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
@@ -7545,31 +7561,31 @@
         <v>21</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>105</v>
@@ -7583,21 +7599,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
@@ -7606,19 +7622,19 @@
         <v>21</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>405</v>
+        <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>406</v>
+        <v>109</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>407</v>
+        <v>110</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>408</v>
+        <v>111</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7656,48 +7672,48 @@
         <v>21</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>21</v>
+        <v>114</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>115</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>410</v>
+        <v>105</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>191</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7720,15 +7736,17 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>310</v>
+        <v>410</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7814,10 +7832,10 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>21</v>
@@ -7829,13 +7847,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7886,10 +7904,10 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>87</v>
@@ -7901,7 +7919,7 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>21</v>
@@ -7910,8 +7928,117 @@
         <v>191</v>
       </c>
     </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>191</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM56">
+  <autoFilter ref="A1:AM57">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7921,7 +8048,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI55">
+  <conditionalFormatting sqref="A2:AI56">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T06:35:14+00:00</t>
+    <t>2026-07-20T14:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:28:37+00:00</t>
+    <t>2026-07-21T08:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:19:16+00:00</t>
+    <t>2026-07-21T08:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:48:20+00:00</t>
+    <t>2026-07-21T09:53:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:53:07+00:00</t>
+    <t>2026-07-21T13:00:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:05+00:00</t>
+    <t>2026-07-27T06:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T06:31:56+00:00</t>
+    <t>2026-07-27T07:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:32:14+00:00</t>
+    <t>2026-07-27T07:43:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:43:34+00:00</t>
+    <t>2026-07-27T08:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T08:58:26+00:00</t>
+    <t>2026-07-27T09:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:29:06+00:00</t>
+    <t>2026-07-27T09:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:54:42+00:00</t>
+    <t>2026-07-27T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:14:55+00:00</t>
+    <t>2026-07-27T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:27:19+00:00</t>
+    <t>2026-07-27T10:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:49:55+00:00</t>
+    <t>2026-07-28T05:51:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T05:51:13+00:00</t>
+    <t>2026-07-28T06:19:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:19:15+00:00</t>
+    <t>2026-07-28T06:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:47:20+00:00</t>
+    <t>2026-07-28T13:00:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:00:26+00:00</t>
+    <t>2026-07-28T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:42:50+00:00</t>
+    <t>2026-07-28T14:03:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:03:46+00:00</t>
+    <t>2026-07-29T06:44:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T06:44:02+00:00</t>
+    <t>2026-07-29T11:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:08:45+00:00</t>
+    <t>2026-07-29T11:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:32:55+00:00</t>
+    <t>2026-07-29T11:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:56:42+00:00</t>
+    <t>2026-07-30T06:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T06:46:32+00:00</t>
+    <t>2026-07-30T07:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:01:31+00:00</t>
+    <t>2026-07-30T10:22:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:22:13+00:00</t>
+    <t>2026-07-31T07:01:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:01:03+00:00</t>
+    <t>2026-07-31T08:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:34:12+00:00</t>
+    <t>2026-07-31T10:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T10:47:24+00:00</t>
+    <t>2026-07-31T12:19:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:19:34+00:00</t>
+    <t>2026-08-03T09:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:14:34+00:00</t>
+    <t>2026-08-03T10:33:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T10:33:06+00:00</t>
+    <t>2026-08-06T10:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4077,7 +4077,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:46:09+00:00</t>
+    <t>2026-08-07T07:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:27:35+00:00</t>
+    <t>2026-08-10T07:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T07:07:45+00:00</t>
+    <t>2026-08-10T09:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T09:07:49+00:00</t>
+    <t>2026-08-10T10:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T10:07:23+00:00</t>
+    <t>2026-08-12T14:05:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1294,7 +1294,7 @@
     <t>AllergyIntolerance.reaction.note</t>
   </si>
   <si>
-    <t>Freitext zur Diagnose für Zusatzinformation</t>
+    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation</t>
   </si>
   <si>
     <t>Additional text about the adverse reaction event not captured in other fields.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T14:05:51+00:00</t>
+    <t>2026-08-12T15:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:02:16+00:00</t>
+    <t>2026-08-13T10:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T10:03:40+00:00</t>
+    <t>2026-08-14T12:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:06:36+00:00</t>
+    <t>2026-08-20T12:53:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:53:18+00:00</t>
+    <t>2026-08-26T13:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$48</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="384">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:50:30+00:00</t>
+    <t>2026-08-28T05:58:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -324,349 +324,175 @@
 </t>
   </si>
   <si>
-    <t>AllergyIntolerance.meta.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
+    <t>AllergyIntolerance.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.meta.extension</t>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension:reported</t>
+  </si>
+  <si>
+    <t>reported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reported}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA Reported (Fremdangabe)</t>
+  </si>
+  <si>
+    <t>Kennzeichnet, ob eine Information fremdberichtet ist (z. B. vom Patienten oder Dritten).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.extension:entered-in-error</t>
+  </si>
+  <si>
+    <t>entered-in-error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-entered-in-error}
+</t>
+  </si>
+  <si>
+    <t>AT ELGA Entered In Error</t>
+  </si>
+  <si>
+    <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
+  </si>
+  <si>
+    <t>AllergyIntolerance.modifierExtension</t>
   </si>
   <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
-</t>
-  </si>
-  <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.meta.security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.meta.tag:diagnosisType</t>
-  </si>
-  <si>
-    <t>diagnosisType</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-diagnosen-type</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.extension:reported</t>
-  </si>
-  <si>
-    <t>reported</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reported}
-</t>
-  </si>
-  <si>
-    <t>AT ELGA Reported (Fremdangabe)</t>
-  </si>
-  <si>
-    <t>Kennzeichnet, ob eine Information fremdberichtet ist (z. B. vom Patienten oder Dritten).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.extension:entered-in-error</t>
-  </si>
-  <si>
-    <t>entered-in-error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-ext-entered-in-error}
-</t>
-  </si>
-  <si>
-    <t>AT ELGA Entered In Error</t>
-  </si>
-  <si>
-    <t>Kennzeichnet, ob eine Information fehlerhaft eingegeben wurde.</t>
-  </si>
-  <si>
-    <t>AllergyIntolerance.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -674,6 +500,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -723,6 +552,9 @@
   <si>
     <t>Refer to [discussion](http://hl7.org/fhir/R4/extensibility.html#Special-Case) if clincalStatus is missing data.
 The data type is CodeableConcept because clinicalStatus has some clinical judgment involved, such that there might need to be more specificity than the required FHIR value set allows. For example, a SNOMED coding might allow for additional specificity.</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/allergyintolerance-clinical|4.0.1</t>
@@ -867,6 +699,9 @@
 When a substance or product code is specified for the 'code' element, the "default" semantic context is that this is a positive statement of an allergy or intolerance (depending on the value of the 'type' element, if present) condition to the specified substance/product.  In the corresponding SNOMED CT allergy model, the specified substance/product is the target (destination) of the "Causative agent" relationship.  The 'substanceExposureRisk' extension is available as a structured and more flexible alternative to the 'code' element for making positive or negative allergy or intolerance statements.  This extension provides the capability to make "no known allergy" (or "no risk of adverse reaction") statements regarding any coded substance/product (including cases when a pre-coordinated "no allergy to x" concept for that substance/product does not exist).  If the 'substanceExposureRisk' extension is present, the AllergyIntolerance.code element SHALL be omitted.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Type of the substance/product, allergy or intolerance condition, or negation/exclusion codes for reporting no known allergies.</t>
@@ -897,10 +732,42 @@
     <t>AllergyIntolerance.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.code.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
     <t>AllergyIntolerance.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -1687,7 +1554,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.27734375" customWidth="true" bestFit="true"/>
@@ -1715,7 +1582,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.50390625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.62109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2202,10 +2069,10 @@
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>101</v>
@@ -2216,7 +2083,9 @@
       <c r="M5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N5" s="2"/>
+      <c r="N5" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -2265,7 +2134,7 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2277,10 +2146,10 @@
         <v>21</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>21</v>
@@ -2298,14 +2167,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>21</v>
@@ -2317,16 +2186,16 @@
         <v>21</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2352,46 +2221,46 @@
         <v>21</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE6" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="AF6" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>105</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>21</v>
@@ -2402,14 +2271,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2425,10 +2294,10 @@
         <v>21</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>118</v>
@@ -2502,7 +2371,7 @@
         <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>21</v>
@@ -2513,21 +2382,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
@@ -2536,19 +2405,19 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2598,22 +2467,22 @@
         <v>21</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>21</v>
@@ -2624,10 +2493,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2638,7 +2507,7 @@
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>21</v>
@@ -2647,20 +2516,18 @@
         <v>21</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>132</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>21</v>
@@ -2697,31 +2564,29 @@
         <v>21</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>21</v>
@@ -2735,12 +2600,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>21</v>
       </c>
@@ -2749,7 +2616,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>21</v>
@@ -2758,20 +2625,18 @@
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -2820,7 +2685,7 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2829,10 +2694,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>21</v>
@@ -2846,12 +2711,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2860,7 +2727,7 @@
         <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2869,20 +2736,18 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
@@ -2907,13 +2772,13 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>21</v>
@@ -2931,7 +2796,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2940,10 +2805,10 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>21</v>
@@ -2957,18 +2822,18 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>79</v>
@@ -2977,24 +2842,26 @@
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O12" s="2"/>
+        <v>154</v>
+      </c>
+      <c r="O12" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -3018,29 +2885,31 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AC12" s="2"/>
-      <c r="AD12" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3052,10 +2921,10 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>21</v>
@@ -3066,23 +2935,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -3094,18 +2961,20 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -3129,11 +2998,13 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -3166,21 +3037,21 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>21</v>
+        <v>163</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>21</v>
+        <v>165</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3188,13 +3059,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>88</v>
@@ -3203,16 +3074,16 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3238,13 +3109,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>21</v>
+        <v>169</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3271,27 +3142,27 @@
         <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>21</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3299,31 +3170,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3349,13 +3220,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3373,7 +3244,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3382,16 +3253,16 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>21</v>
@@ -3399,21 +3270,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>21</v>
@@ -3422,19 +3293,19 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3460,13 +3331,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>21</v>
+        <v>188</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>21</v>
+        <v>189</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3484,7 +3355,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3499,32 +3370,32 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>21</v>
@@ -3533,19 +3404,19 @@
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>107</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3571,13 +3442,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3595,7 +3466,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3607,35 +3478,35 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AM17" t="s" s="2">
-        <v>21</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>21</v>
@@ -3644,18 +3515,20 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3680,91 +3553,93 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>21</v>
+        <v>207</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>21</v>
+        <v>211</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>197</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
@@ -3789,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>21</v>
+        <v>218</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>21</v>
+        <v>219</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3813,40 +3688,38 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>21</v>
+        <v>220</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>21</v>
+        <v>221</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>21</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>21</v>
       </c>
@@ -3867,13 +3740,13 @@
         <v>21</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3924,22 +3797,22 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3950,14 +3823,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3970,26 +3843,24 @@
         <v>21</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
       </c>
@@ -4025,19 +3896,19 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4049,10 +3920,10 @@
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -4063,10 +3934,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4074,10 +3945,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>21</v>
@@ -4089,19 +3960,19 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -4150,7 +4021,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4165,21 +4036,21 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>219</v>
+        <v>21</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>220</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4187,33 +4058,35 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4237,13 +4110,13 @@
         <v>21</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>21</v>
@@ -4261,7 +4134,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4270,31 +4143,31 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>21</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>21</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>21</v>
+        <v>252</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4307,23 +4180,21 @@
         <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>222</v>
+        <v>253</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
@@ -4348,13 +4219,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>234</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4372,40 +4243,40 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>227</v>
+        <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>229</v>
+        <v>257</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>21</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4421,20 +4292,18 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>168</v>
+        <v>260</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4459,13 +4328,13 @@
         <v>21</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>243</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>21</v>
@@ -4483,7 +4352,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4498,25 +4367,25 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>246</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>248</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4532,20 +4401,18 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>168</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4570,13 +4437,13 @@
         <v>21</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>252</v>
+        <v>21</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>21</v>
@@ -4594,13 +4461,13 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>21</v>
@@ -4609,54 +4476,52 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>255</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>272</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4681,13 +4546,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4705,7 +4570,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4720,25 +4585,25 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4754,20 +4619,18 @@
         <v>21</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4792,13 +4655,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>272</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4816,7 +4679,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4831,25 +4694,25 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>275</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4865,18 +4728,20 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>101</v>
+        <v>287</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>102</v>
+        <v>288</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4925,7 +4790,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>104</v>
+        <v>285</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4937,35 +4802,35 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>105</v>
+        <v>291</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>21</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>107</v>
+        <v>21</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4977,16 +4842,16 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>108</v>
+        <v>272</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>109</v>
+        <v>295</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>110</v>
+        <v>296</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>111</v>
+        <v>297</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5024,34 +4889,34 @@
         <v>21</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>115</v>
+        <v>294</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>105</v>
+        <v>298</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
@@ -5062,10 +4927,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5073,10 +4938,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -5085,23 +4950,21 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>141</v>
+        <v>300</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
       </c>
@@ -5149,7 +5012,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5164,21 +5027,21 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>285</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5186,35 +5049,31 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>101</v>
+        <v>306</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>21</v>
       </c>
@@ -5262,13 +5121,13 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
@@ -5277,50 +5136,50 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>293</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>295</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>296</v>
+        <v>224</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>225</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
+        <v>226</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5371,10 +5230,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>227</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>87</v>
@@ -5383,24 +5242,24 @@
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>299</v>
+        <v>228</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>301</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5408,10 +5267,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -5423,13 +5282,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>303</v>
+        <v>132</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>133</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>134</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5468,62 +5327,62 @@
         <v>21</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>306</v>
+        <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>307</v>
+        <v>21</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>21</v>
@@ -5532,13 +5391,13 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5589,68 +5448,72 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>233</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>312</v>
+        <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>313</v>
+        <v>21</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>21</v>
+        <v>318</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I36" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="J36" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>315</v>
+        <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>320</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
       </c>
@@ -5698,50 +5561,50 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>318</v>
+        <v>130</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>320</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>322</v>
+        <v>21</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>21</v>
@@ -5750,15 +5613,17 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5783,13 +5648,13 @@
         <v>21</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>21</v>
+        <v>327</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>21</v>
@@ -5807,7 +5672,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5822,44 +5687,44 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>327</v>
+        <v>21</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>330</v>
+        <v>167</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>331</v>
@@ -5894,13 +5759,13 @@
         <v>21</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>21</v>
+        <v>334</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>21</v>
+        <v>335</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>21</v>
@@ -5918,13 +5783,13 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>21</v>
@@ -5933,10 +5798,10 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>334</v>
+        <v>190</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>335</v>
+        <v>21</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>336</v>
@@ -5951,7 +5816,7 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5970,16 +5835,16 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>315</v>
+        <v>224</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6044,7 +5909,7 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
@@ -6055,10 +5920,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6069,7 +5934,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>21</v>
@@ -6081,7 +5946,7 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>343</v>
+        <v>272</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>344</v>
@@ -6089,9 +5954,7 @@
       <c r="M40" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>346</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6140,13 +6003,13 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6155,21 +6018,21 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AL40" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>348</v>
-      </c>
       <c r="B41" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6177,13 +6040,13 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>21</v>
@@ -6192,15 +6055,17 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>21</v>
@@ -6225,13 +6090,13 @@
         <v>21</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>21</v>
+        <v>351</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>21</v>
+        <v>352</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>21</v>
@@ -6249,13 +6114,13 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>21</v>
@@ -6264,7 +6129,7 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>352</v>
+        <v>209</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -6289,7 +6154,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6301,15 +6166,17 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>101</v>
+        <v>167</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>102</v>
+        <v>354</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6334,13 +6201,13 @@
         <v>21</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>21</v>
+        <v>357</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>21</v>
+        <v>358</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>21</v>
@@ -6358,7 +6225,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>104</v>
+        <v>353</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6370,10 +6237,10 @@
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>105</v>
+        <v>359</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6384,10 +6251,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6395,11 +6262,11 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="G43" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="H43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6410,15 +6277,17 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>108</v>
+        <v>300</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>193</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
@@ -6455,17 +6324,19 @@
         <v>21</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>115</v>
+        <v>360</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6477,10 +6348,10 @@
         <v>21</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>21</v>
+        <v>304</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6489,28 +6360,26 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>356</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>87</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>21</v>
@@ -6519,13 +6388,13 @@
         <v>21</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>357</v>
+        <v>224</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>358</v>
+        <v>225</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>359</v>
+        <v>226</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6576,22 +6445,22 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>115</v>
+        <v>227</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>201</v>
+        <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>21</v>
+        <v>228</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6602,14 +6471,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>361</v>
+        <v>151</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6622,26 +6491,24 @@
         <v>21</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>362</v>
+        <v>230</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>363</v>
+        <v>231</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>21</v>
       </c>
@@ -6677,19 +6544,19 @@
         <v>21</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>21</v>
+        <v>135</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>364</v>
+        <v>233</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6701,10 +6568,10 @@
         <v>21</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6715,10 +6582,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6738,19 +6605,19 @@
         <v>21</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>222</v>
+        <v>367</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6776,13 +6643,13 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>369</v>
+        <v>21</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>370</v>
+        <v>21</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6800,7 +6667,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6815,44 +6682,44 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>21</v>
+        <v>130</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>373</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I47" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K47" t="s" s="2">
-        <v>222</v>
+        <v>272</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>374</v>
@@ -6860,9 +6727,7 @@
       <c r="M47" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N47" t="s" s="2">
-        <v>376</v>
-      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -6887,13 +6752,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>377</v>
+        <v>21</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -6911,13 +6776,13 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
         <v>87</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
@@ -6926,32 +6791,32 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>244</v>
+        <v>377</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>379</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>381</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -6960,20 +6825,18 @@
         <v>21</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>101</v>
+        <v>379</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7022,10 +6885,10 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>87</v>
@@ -7037,1008 +6900,17 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" hidden="true">
-      <c r="A49" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K49" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
-      <c r="P49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q49" s="2"/>
-      <c r="R49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK49" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="AL49" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O54" s="2"/>
-      <c r="P54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O55" s="2"/>
-      <c r="P55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
-      <c r="P56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>191</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM57">
+  <autoFilter ref="A1:AM48">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8048,7 +6920,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI56">
+  <conditionalFormatting sqref="A2:AI47">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T05:58:13+00:00</t>
+    <t>2026-08-28T07:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:25:52+00:00</t>
+    <t>2026-08-28T08:10:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:10:45+00:00</t>
+    <t>2026-08-28T11:38:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -822,7 +822,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -908,7 +908,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
@@ -931,7 +931,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1567,7 +1567,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="198.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="213.203125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:38:22+00:00</t>
+    <t>2026-08-28T12:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:52:33+00:00</t>
+    <t>2026-08-31T10:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:02:50+00:00</t>
+    <t>2026-09-01T06:51:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T06:51:10+00:00</t>
+    <t>2026-09-01T11:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:42:45+00:00</t>
+    <t>2026-09-01T12:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:48:31+00:00</t>
+    <t>2026-09-01T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:57:21+00:00</t>
+    <t>2026-09-03T13:31:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:31:10+00:00</t>
+    <t>2026-09-07T04:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T04:47:29+00:00</t>
+    <t>2026-09-07T06:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T06:52:33+00:00</t>
+    <t>2026-09-07T07:43:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:43:01+00:00</t>
+    <t>2026-09-07T07:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:56:25+00:00</t>
+    <t>2026-09-07T09:23:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:23:06+00:00</t>
+    <t>2026-09-07T10:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:17:45+00:00</t>
+    <t>2026-09-07T10:50:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Allergie in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Allergie in einem internen Dokumentationssystem</t>
   </si>
   <si>
     <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -573,7 +573,7 @@
     <t>AllergyIntolerance.verificationStatus</t>
   </si>
   <si>
-    <t>ToDo; Presumed, gibt es hierzu aktuelle Infos? kardinalität von clinicalStatus &amp; verificationStatus muss noch erarbeitet werden. Möglicher Status; unconfirmed | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Allergie. Möglicher Status; unconfirmed | confirmed | refuted | entered-in-error</t>
   </si>
   <si>
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:50:55+00:00</t>
+    <t>2026-09-08T06:03:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:03:03+00:00</t>
+    <t>2026-09-08T06:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Allergie in einem internen Dokumentationssystem</t>
+    <t>Zuordnung der Allergie in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -544,7 +544,7 @@
 </t>
   </si>
   <si>
-    <t>Status der Allergie; active | inactive | resolved</t>
+    <t>Status der Allergie; mögliche Codes: active | inactive | resolved.</t>
   </si>
   <si>
     <t>The clinical status of the allergy or intolerance.</t>
@@ -573,7 +573,7 @@
     <t>AllergyIntolerance.verificationStatus</t>
   </si>
   <si>
-    <t>Verifizierungsstatus der Allergie. Möglicher Status; unconfirmed | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Allergie; mögliche Codes: unconfirmed | confirmed | refuted | entered-in-error.</t>
   </si>
   <si>
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>
@@ -598,7 +598,7 @@
 Class</t>
   </si>
   <si>
-    <t>Identifikation ob es eine Allergie oder Intoleranz ist</t>
+    <t>Kennzeichnung, ob es sich um eine Allergie oder Intoleranz handelt.</t>
   </si>
   <si>
     <t>Identification of the underlying physiological mechanism for the reaction risk.</t>
@@ -629,7 +629,7 @@
 TypeReaction TypeClass</t>
   </si>
   <si>
-    <t>Differenzierung nach Kontext - Medikamente, Lebensmittel, Umwelt,.. - falls nur med. rele. dann ist es nicht notwendig, fachlich klären</t>
+    <t>ToDo - falls nur med. rele. dann ist es nicht notwendig, fachlich klären: Differenzierung nach Kontext z. B. Medikamente, Lebensmittel oder Umwelt.</t>
   </si>
   <si>
     <t>Category of the identified substance.</t>
@@ -657,7 +657,7 @@
 SeriousnessContra-indicationRisk</t>
   </si>
   <si>
-    <t>Einschätzung der Schwere (Anaphylaxie)</t>
+    <t>Einschätzung des Schweregrads, z. B. im Hinblick auf eine Anaphylaxie.</t>
   </si>
   <si>
     <t>Estimate of the potential clinical harm, or seriousness, of the reaction to the identified substance.</t>
@@ -688,7 +688,7 @@
 </t>
   </si>
   <si>
-    <t>Allergiecode, Text verboten</t>
+    <t>Allergiecode; Freitext ist nicht zulässig.</t>
   </si>
   <si>
     <t>Code for an allergy or intolerance statement (either a positive or a negated/excluded statement).  This may be a code for a substance or pharmaceutical product that is considered to be responsible for the adverse reaction risk (e.g., "Latex"), an allergy or intolerance condition (e.g., "Latex allergy"), or a negated/excluded code for a specific substance or class (e.g., "No latex allergy") or a general or categorical negated statement (e.g.,  "No known allergy", "No known drug allergies").  Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -826,7 +826,7 @@
 </t>
   </si>
   <si>
-    <t>Betroffene Person, auf die sich die Allergie bezieht</t>
+    <t>Betroffene Person, auf die sich die Allergie bezieht.</t>
   </si>
   <si>
     <t>The patient who has the allergy or intolerance.</t>
@@ -848,7 +848,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontakt</t>
+    <t>Behandlungskontakt.</t>
   </si>
   <si>
     <t>The encounter when the allergy or intolerance was asserted.</t>
@@ -867,7 +867,7 @@
 AgePeriodRangestring</t>
   </si>
   <si>
-    <t>Erstes Aufzeichnungsdatum der Allergie(symptomatik)</t>
+    <t>Erstes Aufzeichnungsdatum der Allergie bzw. Allergiesymptomatik.</t>
   </si>
   <si>
     <t>Estimated or actual date,  date-time, or age when allergy or intolerance was identified.</t>
@@ -886,7 +886,7 @@
 </t>
   </si>
   <si>
-    <t>Dokumentationsdatum</t>
+    <t>Dokumentationsdatum.</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
@@ -912,7 +912,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, die die Allergie ins System erfasst/dokumentiert</t>
+    <t>Gesundheitsdiensteanbieter, der die Allergie im System erfasst bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -935,7 +935,7 @@
 </t>
   </si>
   <si>
-    <t>Person (fachliche Quelle + related Person oder Patient selbst), die/der die Allergie bestätigt</t>
+    <t>Quelle der Information zur Allergie, z. B. Patient, behandelnde Person oder Dritter.</t>
   </si>
   <si>
     <t>The source of the information about the allergy that is recorded.</t>
@@ -956,7 +956,7 @@
     <t>AllergyIntolerance.lastOccurrence</t>
   </si>
   <si>
-    <t>Letztes Auftreten der Symptomatik - siehe manifestation</t>
+    <t>Letztes Auftreten der Symptomatik; siehe Manifestation.</t>
   </si>
   <si>
     <t>Represents the date and/or time of the last known occurrence of a reaction event.</t>
@@ -975,7 +975,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen oder Freitext zur Allergie wird in reaction beschrieben</t>
+    <t>Zusätzliche Informationen; Freitext wird in reaction beschrieben.</t>
   </si>
   <si>
     <t>Additional narrative about the propensity for the Adverse Reaction, not captured in other fields.</t>
@@ -994,7 +994,7 @@
 </t>
   </si>
   <si>
-    <t>Details über die Allergiereaktion</t>
+    <t>Details zur allergischen Reaktion.</t>
   </si>
   <si>
     <t>Details about each adverse reaction event linked to exposure to the identified substance.</t>
@@ -1019,7 +1019,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitlicher Verlauf der Manifestation</t>
+    <t>Zeitlicher Verlauf der Manifestation.</t>
   </si>
   <si>
     <t>Zeitlicher Verlauf der Manifestation (&lt;6h, 6-24h, &gt;24h, unknown)</t>
@@ -1045,7 +1045,7 @@
     <t>AllergyIntolerance.reaction.substance</t>
   </si>
   <si>
-    <t>Spezifische Substanz die zur Allergie führt, wird in allergyintoleranz.code gelöst</t>
+    <t>Spezifische Substanz, die zur Allergie führt; wird über AllergyIntolerance.code abgebildet.</t>
   </si>
   <si>
     <t>Identification of the specific substance (or pharmaceutical product) considered to be responsible for the Adverse Reaction event. Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -1070,7 +1070,7 @@
 Signs</t>
   </si>
   <si>
-    <t>Aufgezeichnete klinische allergische Symptome</t>
+    <t>Aufgezeichnete klinische Symptome der allergischen Reaktion.</t>
   </si>
   <si>
     <t>Clinical symptoms and/or signs that are observed or associated with the adverse reaction event.</t>
@@ -1095,7 +1095,7 @@
 Text</t>
   </si>
   <si>
-    <t>Textbasierte Zusammenfassung der allergischen Reaktion</t>
+    <t>Textbasierte Zusammenfassung der allergischen Reaktion.</t>
   </si>
   <si>
     <t>Text description about the reaction as a whole, including details of the manifestation if required.</t>
@@ -1110,7 +1110,7 @@
     <t>AllergyIntolerance.reaction.onset</t>
   </si>
   <si>
-    <t>Beginn der Reaktion</t>
+    <t>Beginn der Reaktion.</t>
   </si>
   <si>
     <t>Record of the date and/or time of the onset of the Reaction.</t>
@@ -1122,7 +1122,7 @@
     <t>AllergyIntolerance.reaction.severity</t>
   </si>
   <si>
-    <t>Beschreibt ob die Reaktion mild, moderat,... war</t>
+    <t>Schweregrad der Reaktion, z. B. mild oder moderat.</t>
   </si>
   <si>
     <t>Clinical assessment of the severity of the reaction event as a whole, potentially considering multiple different manifestations.</t>
@@ -1140,7 +1140,7 @@
     <t>AllergyIntolerance.reaction.exposureRoute</t>
   </si>
   <si>
-    <t>Art der Exposition der betroffenen Person gegenüber der Substanz</t>
+    <t>Art der Exposition der betroffenen Person gegenüber der Substanz.</t>
   </si>
   <si>
     <t>Identification of the route by which the subject was exposed to the substance.</t>
@@ -1161,7 +1161,7 @@
     <t>AllergyIntolerance.reaction.note</t>
   </si>
   <si>
-    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation</t>
+    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation.</t>
   </si>
   <si>
     <t>Additional text about the adverse reaction event not captured in other fields.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:16:43+00:00</t>
+    <t>2026-09-08T06:28:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -912,7 +912,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Allergie im System erfasst bzw. dokumentiert hat.</t>
+    <t>GDA, der die Allergie im System erfasst bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:28:20+00:00</t>
+    <t>2026-09-08T06:46:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:46:13+00:00</t>
+    <t>2026-09-08T10:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:19:13+00:00</t>
+    <t>2026-09-08T10:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:46:31+00:00</t>
+    <t>2026-09-08T11:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:50:41+00:00</t>
+    <t>2026-09-08T12:56:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:56:54+00:00</t>
+    <t>2026-09-09T04:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T04:29:28+00:00</t>
+    <t>2026-09-09T07:41:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T07:41:46+00:00</t>
+    <t>2026-09-09T08:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T08:03:40+00:00</t>
+    <t>2026-09-09T09:18:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:18:29+00:00</t>
+    <t>2026-09-09T14:48:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:48:33+00:00</t>
+    <t>2026-09-10T08:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:40:11+00:00</t>
+    <t>2026-09-10T09:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:01:10+00:00</t>
+    <t>2026-09-10T09:35:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:35:03+00:00</t>
+    <t>2026-09-10T09:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:50:09+00:00</t>
+    <t>2026-09-10T10:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:02:23+00:00</t>
+    <t>2026-09-10T11:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:15:10+00:00</t>
+    <t>2026-09-10T11:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:24:50+00:00</t>
+    <t>2026-09-10T11:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:47:23+00:00</t>
+    <t>2026-09-10T14:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:22:40+00:00</t>
+    <t>2026-09-11T07:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-allergyintolerance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:57:50+00:00</t>
+    <t>2026-09-11T08:25:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
